--- a/corr_matrix/residual_exam2C_1PL.xlsx
+++ b/corr_matrix/residual_exam2C_1PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2C01</t>
@@ -520,49 +525,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02843750734590492</v>
+        <v>-0.02843360207519735</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009927689176073583</v>
+        <v>0.009906781324304928</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09879584170646988</v>
+        <v>0.09878605081295308</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3012853703572983</v>
+        <v>-0.3012674791816929</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03448192769617834</v>
+        <v>0.03450448670569203</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1900635986705304</v>
+        <v>-0.1900459222269824</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01125487238870559</v>
+        <v>0.01125932897910456</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1706374258359162</v>
+        <v>-0.1706235788189636</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1546310507751968</v>
+        <v>-0.1546433704053602</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.08105280063689571</v>
+        <v>-0.08105594789403418</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1933562967375543</v>
+        <v>-0.1933562599456743</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.127924579775567</v>
+        <v>-0.1279293513800748</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.04197699076112056</v>
+        <v>-0.04199535726402885</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2878969932426251</v>
+        <v>-0.2878800575606884</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.002049374379231531</v>
+        <v>0.002065370262323066</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +577,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02843750734590492</v>
+        <v>-0.02843360207519735</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1596386067921264</v>
+        <v>-0.1596437892452612</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07379266903769258</v>
+        <v>0.0737965084535053</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1035783283668582</v>
+        <v>-0.103592821264731</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.08957333637292628</v>
+        <v>-0.08956080189739722</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04616158642923623</v>
+        <v>0.04615359179956565</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2597078479975159</v>
+        <v>0.2597051049403333</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1953944429665244</v>
+        <v>-0.1953878724823513</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1744373678959321</v>
+        <v>-0.1744380447193019</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1614051905661564</v>
+        <v>-0.1613926174311195</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1134011878310665</v>
+        <v>-0.1133975810675841</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1208125797457323</v>
+        <v>-0.1208179632038642</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2992166625688172</v>
+        <v>-0.2992188378395738</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07666961774299881</v>
+        <v>0.07665525683041401</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1745661526652642</v>
+        <v>-0.1745746329577106</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009927689176073583</v>
+        <v>0.009906781324304928</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1596386067921264</v>
+        <v>-0.1596437892452612</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1421259036887728</v>
+        <v>-0.1421286043372614</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.005117730925529571</v>
+        <v>-0.005131680495445683</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.01969697899247913</v>
+        <v>-0.0197056987890815</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1488649785122098</v>
+        <v>-0.148869870912474</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1062811690833526</v>
+        <v>-0.1062945669023058</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05171973914781666</v>
+        <v>0.05171161915610391</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1517131852726812</v>
+        <v>-0.1517193925353049</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1606102143703568</v>
+        <v>-0.1606026416703189</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03422633529636067</v>
+        <v>0.03422289880011745</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08564397734209431</v>
+        <v>0.08563714198525393</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08511045890655219</v>
+        <v>0.08511223796586688</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.07825902200703906</v>
+        <v>-0.07826864025074755</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.09136506936075708</v>
+        <v>-0.0913734057703125</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09879584170646988</v>
+        <v>0.09878605081295308</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07379266903769258</v>
+        <v>0.0737965084535053</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1421259036887728</v>
+        <v>-0.1421286043372614</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01433595912968748</v>
+        <v>-0.01433779276959719</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.101609258102779</v>
+        <v>-0.1016052006344568</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.05282088144252831</v>
+        <v>-0.05281557010420185</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.226095930469676</v>
+        <v>-0.2261052630661065</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.162476893439228</v>
+        <v>-0.1624798288521468</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01199091047480886</v>
+        <v>-0.01201050901988681</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.04777214323010505</v>
+        <v>-0.04777352200914687</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2393119958508611</v>
+        <v>-0.2393177901707433</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2016930452686193</v>
+        <v>-0.2017026366939618</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03125014053795591</v>
+        <v>0.0312370295802052</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1137491888261617</v>
+        <v>0.1137492754285689</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01123890510729353</v>
+        <v>0.01124347521223161</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +742,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.3012853703572983</v>
+        <v>-0.3012674791816929</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1035783283668582</v>
+        <v>-0.103592821264731</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.005117730925529571</v>
+        <v>-0.005131680495445683</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01433595912968748</v>
+        <v>-0.01433779276959719</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0325174994400201</v>
+        <v>-0.03250776100700137</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.04709251166531964</v>
+        <v>-0.04710210430900597</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2053433068461231</v>
+        <v>-0.2053531202920436</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.02622036926383871</v>
+        <v>-0.02621661922587229</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01885787409471274</v>
+        <v>-0.01885175636849399</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.04088339487249665</v>
+        <v>-0.04088053880548897</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05966209914191369</v>
+        <v>-0.05966784830216531</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.07737782930015315</v>
+        <v>-0.07739097161209016</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02900461239856588</v>
+        <v>0.02900661416669047</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05638347330222026</v>
+        <v>0.05637418496869249</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1107346286661529</v>
+        <v>-0.1107452905978409</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03448192769617834</v>
+        <v>0.03450448670569203</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.08957333637292628</v>
+        <v>-0.08956080189739722</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.01969697899247913</v>
+        <v>-0.0197056987890815</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.101609258102779</v>
+        <v>-0.1016052006344568</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0325174994400201</v>
+        <v>-0.03250776100700137</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3515529812704495</v>
+        <v>-0.3515406508948128</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1332618762445997</v>
+        <v>-0.1332495991497898</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.05840674896800164</v>
+        <v>-0.05838786010227486</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1262978306683014</v>
+        <v>-0.1263026405028665</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1079323367560046</v>
+        <v>-0.1079217251866122</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.06269264563479089</v>
+        <v>-0.06268240025779694</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06675025686888054</v>
+        <v>-0.06674476326950182</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.001612278543267379</v>
+        <v>-0.001623457378479043</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.06714262774638625</v>
+        <v>-0.06713750938806191</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1587482517592564</v>
+        <v>-0.1587340394479156</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +852,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1900635986705304</v>
+        <v>-0.1900459222269824</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04616158642923623</v>
+        <v>0.04615359179956565</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1488649785122098</v>
+        <v>-0.148869870912474</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.05282088144252831</v>
+        <v>-0.05281557010420185</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.04709251166531964</v>
+        <v>-0.04710210430900597</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3515529812704495</v>
+        <v>-0.3515406508948128</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1373926364843852</v>
+        <v>0.1373944136885666</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1813820134559903</v>
+        <v>-0.1813727067095147</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09885981219634901</v>
+        <v>0.09887423827221249</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.180925970975024</v>
+        <v>-0.1809188099080482</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1221892180430683</v>
+        <v>-0.122187881106383</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04978619312666353</v>
+        <v>0.04978417216532333</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2653455711536253</v>
+        <v>-0.265341972893592</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.08527866727353366</v>
+        <v>-0.08528976550843188</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2620557399952271</v>
+        <v>0.262048364056336</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +907,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01125487238870559</v>
+        <v>0.01125932897910456</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2597078479975159</v>
+        <v>0.2597051049403333</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1062811690833526</v>
+        <v>-0.1062945669023058</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.226095930469676</v>
+        <v>-0.2261052630661065</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2053433068461231</v>
+        <v>-0.2053531202920436</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1332618762445997</v>
+        <v>-0.1332495991497898</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1373926364843852</v>
+        <v>0.1373944136885666</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2020907483072342</v>
+        <v>-0.2020907037794421</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1384878993314773</v>
+        <v>0.1384813238551878</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1137974534538504</v>
+        <v>-0.1137943517565786</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.04223076027455871</v>
+        <v>-0.04223514669112759</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.249599720337344</v>
+        <v>-0.2496140640296285</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1169387750673175</v>
+        <v>-0.1169490935783569</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1661919488196797</v>
+        <v>-0.1661996419917373</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.01600833364869832</v>
+        <v>-0.01600957046691184</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +962,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1706374258359162</v>
+        <v>-0.1706235788189636</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1953944429665244</v>
+        <v>-0.1953878724823513</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05171973914781666</v>
+        <v>0.05171161915610391</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.162476893439228</v>
+        <v>-0.1624798288521468</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.02622036926383871</v>
+        <v>-0.02621661922587229</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.05840674896800164</v>
+        <v>-0.05838786010227486</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1813820134559903</v>
+        <v>-0.1813727067095147</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2020907483072342</v>
+        <v>-0.2020907037794421</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1328021306891004</v>
+        <v>0.132794835732801</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1233233541828288</v>
+        <v>0.1233288565140105</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1095078077478865</v>
+        <v>0.1095096814115988</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.06587466987534837</v>
+        <v>-0.06587817295116379</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1076348031679908</v>
+        <v>-0.1076448049508195</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.07385580102950501</v>
+        <v>-0.07385351119244342</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1637870595987205</v>
+        <v>-0.1637772557322047</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1017,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1546310507751968</v>
+        <v>-0.1546433704053602</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1744373678959321</v>
+        <v>-0.1744380447193019</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1517131852726812</v>
+        <v>-0.1517193925353049</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01199091047480886</v>
+        <v>-0.01201050901988681</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.01885787409471274</v>
+        <v>-0.01885175636849399</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1262978306683014</v>
+        <v>-0.1263026405028665</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09885981219634901</v>
+        <v>0.09887423827221249</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1384878993314773</v>
+        <v>0.1384813238551878</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1328021306891004</v>
+        <v>0.132794835732801</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.06730820959066357</v>
+        <v>-0.06732150722642304</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.06680546672665516</v>
+        <v>-0.0668178747567596</v>
       </c>
       <c r="N11" t="n">
-        <v>0.02275850432245744</v>
+        <v>0.02274911007104477</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.05412988365976569</v>
+        <v>-0.05414947478335983</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1972544766899729</v>
+        <v>-0.1972491242809237</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.006007873997590078</v>
+        <v>0.006017533378553171</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.08105280063689571</v>
+        <v>-0.08105594789403418</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1614051905661564</v>
+        <v>-0.1613926174311195</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1606102143703568</v>
+        <v>-0.1606026416703189</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04777214323010505</v>
+        <v>-0.04777352200914687</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.04088339487249665</v>
+        <v>-0.04088053880548897</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1079323367560046</v>
+        <v>-0.1079217251866122</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.180925970975024</v>
+        <v>-0.1809188099080482</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1137974534538504</v>
+        <v>-0.1137943517565786</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1233233541828288</v>
+        <v>0.1233288565140105</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.06730820959066357</v>
+        <v>-0.06732150722642304</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1185143855861848</v>
+        <v>-0.118507834848841</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1581674796954968</v>
+        <v>0.1581720784244437</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3048281569298386</v>
+        <v>0.3048194055254682</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.03151988225719139</v>
+        <v>-0.0315194885809801</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2119826513179685</v>
+        <v>-0.2119743213905139</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1933562967375543</v>
+        <v>-0.1933562599456743</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1134011878310665</v>
+        <v>-0.1133975810675841</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03422633529636067</v>
+        <v>0.03422289880011745</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2393119958508611</v>
+        <v>-0.2393177901707433</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.05966209914191369</v>
+        <v>-0.05966784830216531</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.06269264563479089</v>
+        <v>-0.06268240025779694</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1221892180430683</v>
+        <v>-0.122187881106383</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04223076027455871</v>
+        <v>-0.04223514669112759</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1095078077478865</v>
+        <v>0.1095096814115988</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.06680546672665516</v>
+        <v>-0.0668178747567596</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1185143855861848</v>
+        <v>-0.118507834848841</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02632571915404269</v>
+        <v>0.0263213216198497</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1358019749739028</v>
+        <v>0.1357936334896155</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.0767853625577273</v>
+        <v>-0.07679158097779004</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.03683394842879713</v>
+        <v>-0.03683236889793915</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.127924579775567</v>
+        <v>-0.1279293513800748</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1208125797457323</v>
+        <v>-0.1208179632038642</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08564397734209431</v>
+        <v>0.08563714198525393</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2016930452686193</v>
+        <v>-0.2017026366939618</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.07737782930015315</v>
+        <v>-0.07739097161209016</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.06675025686888054</v>
+        <v>-0.06674476326950182</v>
       </c>
       <c r="H14" t="n">
-        <v>0.04978619312666353</v>
+        <v>0.04978417216532333</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.249599720337344</v>
+        <v>-0.2496140640296285</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.06587466987534837</v>
+        <v>-0.06587817295116379</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02275850432245744</v>
+        <v>0.02274911007104477</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1581674796954968</v>
+        <v>0.1581720784244437</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02632571915404269</v>
+        <v>0.0263213216198497</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.07368985364375576</v>
+        <v>0.07368412790909239</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.09641189750390412</v>
+        <v>-0.09642296024395462</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1514457914422246</v>
+        <v>-0.1514519175928975</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1237,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04197699076112056</v>
+        <v>-0.04199535726402885</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.2992166625688172</v>
+        <v>-0.2992188378395738</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08511045890655219</v>
+        <v>0.08511223796586688</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03125014053795591</v>
+        <v>0.0312370295802052</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02900461239856588</v>
+        <v>0.02900661416669047</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.001612278543267379</v>
+        <v>-0.001623457378479043</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2653455711536253</v>
+        <v>-0.265341972893592</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1169387750673175</v>
+        <v>-0.1169490935783569</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1076348031679908</v>
+        <v>-0.1076448049508195</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.05412988365976569</v>
+        <v>-0.05414947478335983</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3048281569298386</v>
+        <v>0.3048194055254682</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1358019749739028</v>
+        <v>0.1357936334896155</v>
       </c>
       <c r="N15" t="n">
-        <v>0.07368985364375576</v>
+        <v>0.07368412790909239</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.01706154629146548</v>
+        <v>-0.01705762439569323</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.23058100792057</v>
+        <v>-0.2305794867197914</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2878969932426251</v>
+        <v>-0.2878800575606884</v>
       </c>
       <c r="C16" t="n">
-        <v>0.07666961774299881</v>
+        <v>0.07665525683041401</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07825902200703906</v>
+        <v>-0.07826864025074755</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1137491888261617</v>
+        <v>0.1137492754285689</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05638347330222026</v>
+        <v>0.05637418496869249</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.06714262774638625</v>
+        <v>-0.06713750938806191</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.08527866727353366</v>
+        <v>-0.08528976550843188</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1661919488196797</v>
+        <v>-0.1661996419917373</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.07385580102950501</v>
+        <v>-0.07385351119244342</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1972544766899729</v>
+        <v>-0.1972491242809237</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.03151988225719139</v>
+        <v>-0.0315194885809801</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0767853625577273</v>
+        <v>-0.07679158097779004</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.09641189750390412</v>
+        <v>-0.09642296024395462</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.01706154629146548</v>
+        <v>-0.01705762439569323</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1090093252065363</v>
+        <v>-0.1090215506567448</v>
       </c>
     </row>
     <row r="17">
@@ -1342,49 +1347,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.002049374379231531</v>
+        <v>0.002065370262323066</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1745661526652642</v>
+        <v>-0.1745746329577106</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09136506936075708</v>
+        <v>-0.0913734057703125</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01123890510729353</v>
+        <v>0.01124347521223161</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1107346286661529</v>
+        <v>-0.1107452905978409</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1587482517592564</v>
+        <v>-0.1587340394479156</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2620557399952271</v>
+        <v>0.262048364056336</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.01600833364869832</v>
+        <v>-0.01600957046691184</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1637870595987205</v>
+        <v>-0.1637772557322047</v>
       </c>
       <c r="K17" t="n">
-        <v>0.006007873997590078</v>
+        <v>0.006017533378553171</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2119826513179685</v>
+        <v>-0.2119743213905139</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.03683394842879713</v>
+        <v>-0.03683236889793915</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1514457914422246</v>
+        <v>-0.1514519175928975</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.23058100792057</v>
+        <v>-0.2305794867197914</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1090093252065363</v>
+        <v>-0.1090215506567448</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
